--- a/outputs/personnel-import-template.xlsx
+++ b/outputs/personnel-import-template.xlsx
@@ -2,28 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Особовий склад" sheetId="1" r:id="Rf87289c3264c4621"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів ОС" sheetId="2" r:id="Re1c0479989d54760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кастомні поля ОС" sheetId="3" r:id="R97d508f440c64131"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Автомобілі" sheetId="4" r:id="Rf10b76d0d1bf4498"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів автомобілів" sheetId="5" r:id="Rea7422d7e80848c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кастомні поля автомобілів" sheetId="6" r:id="R693f4a2597ef4918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Екіпажі" sheetId="7" r:id="R7fccf83055ee40e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів екіпажів" sheetId="8" r:id="R41ec84c21a7a4612"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Позиції" sheetId="9" r:id="R42baedf330854f78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів позицій" sheetId="10" r:id="R10ae2779e5fc47a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Склад екіпажів" sheetId="11" r:id="R3b25a0c78a564f03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа складу екіпажів" sheetId="12" r:id="R235a463c6cb344d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Генератори" sheetId="13" r:id="Rad2feaac620d4e7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів генераторів" sheetId="14" r:id="R31e9678c917c41e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="БпЛА" sheetId="15" r:id="R33c642d48b46480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів БпЛА" sheetId="16" r:id="R4b66123db94149a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Зв’язок" sheetId="17" r:id="R4c65a542aa894004"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів зв’язку" sheetId="18" r:id="R08472e590eb24112"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Зброя та БК" sheetId="19" r:id="Ra0e0934235dd413b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів зброї та БК" sheetId="20" r:id="R42dddb07c3004d82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Інциденти" sheetId="21" r:id="R9ce0b16313ae4c20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів інцидентів" sheetId="22" r:id="R02cda034b8ed4ad4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Особовий склад" sheetId="1" r:id="Ra6f1b6a76b9d4766"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів ОС" sheetId="2" r:id="R52df6b9a2d0c45c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кастомні поля ОС" sheetId="3" r:id="R66003f48a7494e49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Автомобілі" sheetId="4" r:id="R8a824570eaf54b6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів автомобілів" sheetId="5" r:id="Rff481608ce804647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кастомні поля автомобілів" sheetId="6" r:id="R23c8f5f9e423444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Екіпажі" sheetId="7" r:id="R0ed3093910714c7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів екіпажів" sheetId="8" r:id="Raf75ddaa005946e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Позиції" sheetId="9" r:id="R9daceaa41ec74942"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів позицій" sheetId="10" r:id="Rf091308fd4ce43e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Склад екіпажів" sheetId="11" r:id="R6b67a34b5b9b4b93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа складу екіпажів" sheetId="12" r:id="R280258f773d64338"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Генератори" sheetId="13" r:id="R78b7efe6525842a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів генераторів" sheetId="14" r:id="R44e2fe0b406048b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="БпЛА" sheetId="15" r:id="R11dc17a683fe424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів БпЛА" sheetId="16" r:id="R3e32ab635d594853"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Зв’язок" sheetId="17" r:id="Rd74b8fd97ba04e92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів зв’язку" sheetId="18" r:id="R9e1e6e7049bb4062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Зброя та БК" sheetId="19" r:id="R62a11e30baf64eb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів зброї та БК" sheetId="20" r:id="R22c697e358694a2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Інциденти" sheetId="21" r:id="R8ba75ce7cc3347fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мапа полів інцидентів" sheetId="22" r:id="Reb12856e6bca49c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фактичний склад екіпажів" sheetId="23" r:id="R6bcc125a9c454305"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +35,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -50,8 +51,18 @@
       <x:color rgb="FF31523A"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -66,6 +77,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F3EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -161,7 +177,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -213,6 +229,9 @@
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -2277,6 +2296,42 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="25" t="str">
+        <x:v>crew_name</x:v>
+      </x:c>
+      <x:c r="B1" s="25" t="str">
+        <x:v>personnel_tax_id</x:v>
+      </x:c>
+      <x:c r="C1" s="25" t="str">
+        <x:v>personnel_full_name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="23" t="str">
+        <x:v>crew_name</x:v>
+      </x:c>
+      <x:c r="B2" s="23" t="str">
+        <x:v>personnel_tax_id</x:v>
+      </x:c>
+      <x:c r="C2" s="23" t="str">
+        <x:v>personnel_full_name</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
